--- a/data/alertas.xlsx
+++ b/data/alertas.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1058,6 +1058,40 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46308.83702546296</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pore Refiner Creamy Skincare 70 Pads com Ácido Salicílico</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>132.04</v>
+      </c>
+      <c r="D20" t="n">
+        <v>140</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>🐾 BOTE CERTEIRO! Pore Refiner Creamy Skincare 70 Pads com Ácido Salicílico caiu 0,0% e está em R$ 132,04. Pode me agradecer com sachê.
+🛍️ Pore Refiner Creamy Skincare 70 Pads com Ácido Salicílico
+💰 Preço atual: R$ 132,04
+🎯 Meta: R$ 140,00
+📉 Variação: ▲ 0,0% desde a última espiada
+🔗 Ver a presa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/alertas.xlsx
+++ b/data/alertas.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -996,7 +996,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pore Refiner Creamy Skincare 70 Pads com Ácido Salicílico</t>
+          <t>Creme Skincare com Ácido Salicílico | Creamy</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pore Refiner Creamy Skincare 70 Pads com Ácido Salicílico</t>
+          <t>Creme Skincare com Ácido Salicílico | Creamy</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pore Refiner Creamy Skincare 70 Pads com Ácido Salicílico</t>
+          <t>Creme Skincare com Ácido Salicílico | Creamy</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1092,6 +1092,346 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46309.89386574074</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Headset Razer BlackShark V2 X</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>359.99</v>
+      </c>
+      <c r="D21" t="n">
+        <v>365</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>🐾 NHAC! Headset Razer BlackShark V2 X chegou na meta: R$ 359,99. Pode deixar o petisco no pote.
+🛍️ Headset Razer BlackShark V2 X
+💰 Preço atual: R$ 359,99
+🎯 Meta: R$ 365,00
+📉 Variação: ▲ 0,0% desde a última espiada
+🔗 Ver a presa</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46309.89394675926</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Creme Skincare com Ácido Salicílico | Creamy</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>132.04</v>
+      </c>
+      <c r="D22" t="n">
+        <v>140</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>🐾 PEGUEI! Creme Skincare com Ácido Salicílico | Creamy a R$ 132,04 (0,0%). Quero meu sachê de salmão.
+🛍️ Creme Skincare com Ácido Salicílico | Creamy
+💰 Preço atual: R$ 132,04
+🎯 Meta: R$ 140,00
+📉 Variação: ▲ 0,0% desde a última espiada
+🔗 Ver a presa</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46309.89585648148</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Headset Razer BlackShark V2 X</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>359.99</v>
+      </c>
+      <c r="D23" t="n">
+        <v>365</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>🐾 PRESA ABATIDA! Headset Razer BlackShark V2 X por R$ 359,99. Eu sou incrível, eu sei. 😼
+🛍️ Headset Razer BlackShark V2 X
+💰 Preço atual: R$ 359,99
+🎯 Meta: R$ 365,00
+📉 Variação: ▲ 0,0% desde a última espiada
+🔗 Ver a presa</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46309.89592592593</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Creme Skincare com Ácido Salicílico | Creamy</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>132.04</v>
+      </c>
+      <c r="D24" t="n">
+        <v>140</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>🐾 PEGUEI! Creme Skincare com Ácido Salicílico | Creamy a R$ 132,04 (0,0%). Quero meu sachê de salmão.
+🛍️ Creme Skincare com Ácido Salicílico | Creamy
+💰 Preço atual: R$ 132,04
+🎯 Meta: R$ 140,00
+📉 Variação: ▲ 0,0% desde a última espiada
+🔗 Ver a presa</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46309.89744212963</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Headset Razer BlackShark V2 X</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>359.99</v>
+      </c>
+      <c r="D25" t="n">
+        <v>365</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>🐾 PEGUEI! Headset Razer BlackShark V2 X a R$ 359,99 (0,0%). Quero meu sachê de salmão.
+🛍️ Headset Razer BlackShark V2 X
+💰 Preço atual: R$ 359,99
+🎯 Meta: R$ 365,00
+📉 Variação: ▲ 0,0% desde a última espiada
+🔗 Ver a presa</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46309.8975</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Creme Skincare com Ácido Salicílico | Creamy</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>132.04</v>
+      </c>
+      <c r="D26" t="n">
+        <v>140</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>🐾 PEGUEI! Creme Skincare com Ácido Salicílico | Creamy a R$ 132,04 (0,0%). Quero meu sachê de salmão.
+🛍️ Creme Skincare com Ácido Salicílico | Creamy
+💰 Preço atual: R$ 132,04
+🎯 Meta: R$ 140,00
+📉 Variação: ▲ 0,0% desde a última espiada
+🔗 Ver a presa</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46309.89905092592</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Headset Razer BlackShark V2 X</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>359.99</v>
+      </c>
+      <c r="D27" t="n">
+        <v>365</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>🐾 NHAC! Headset Razer BlackShark V2 X chegou na meta: R$ 359,99. Pode deixar o petisco no pote.
+🛍️ Headset Razer BlackShark V2 X
+💰 Preço atual: R$ 359,99
+🎯 Meta: R$ 365,00
+📉 Variação: ▲ 0,0% desde a última espiada
+🔗 Ver a presa</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46309.89909722222</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Creme Skincare com Ácido Salicílico | Creamy</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>132.04</v>
+      </c>
+      <c r="D28" t="n">
+        <v>140</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>🐾 PEGUEI! Creme Skincare com Ácido Salicílico | Creamy a R$ 132,04 (0,0%). Quero meu sachê de salmão.
+🛍️ Creme Skincare com Ácido Salicílico | Creamy
+💰 Preço atual: R$ 132,04
+🎯 Meta: R$ 140,00
+📉 Variação: ▲ 0,0% desde a última espiada
+🔗 Ver a presa</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46309.89951388889</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Headset Razer BlackShark V2 X</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>359.99</v>
+      </c>
+      <c r="D29" t="n">
+        <v>365</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>🐾 BOTE CERTEIRO! Headset Razer BlackShark V2 X caiu 0,0% e está em R$ 359,99. Pode me agradecer com sachê.
+🛍️ Headset Razer BlackShark V2 X
+💰 Preço atual: R$ 359,99
+🎯 Meta: R$ 365,00
+📉 Variação: ▲ 0,0% desde a última espiada
+🔗 Ver a presa</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46309.89957175926</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Creme Skincare com Ácido Salicílico | Creamy</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>132.04</v>
+      </c>
+      <c r="D30" t="n">
+        <v>140</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>🐾 BOTE CERTEIRO! Creme Skincare com Ácido Salicílico | Creamy caiu 0,0% e está em R$ 132,04. Pode me agradecer com sachê.
+🛍️ Creme Skincare com Ácido Salicílico | Creamy
+💰 Preço atual: R$ 132,04
+🎯 Meta: R$ 140,00
+📉 Variação: ▲ 0,0% desde a última espiada
+🔗 Ver a presa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
